--- a/Cplusplus/07. CONCURRENCY & MULTITHREADING.xlsx
+++ b/Cplusplus/07. CONCURRENCY & MULTITHREADING.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="735">
   <si>
     <t>1. Threading Basics</t>
   </si>
@@ -1407,7 +1407,7 @@
   </si>
   <si>
     <r>
-      <t>Định nghĩa:</t>
+      <t>ƯU ĐIỂM:</t>
     </r>
     <r>
       <rPr>
@@ -1418,12 +1418,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Mutual Exclusion object, đảm bảo chỉ một thread truy cập critical section tại một thời điểm.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t xml:space="preserve"> Nhanh hơn mutex cho các operation đơn giản, lock-free</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
     </r>
     <r>
       <rPr>
@@ -1434,12 +1434,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Mutex cho phép cùng một thread lock nhiều lần (reentrant).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
+      <t xml:space="preserve"> Lock-free stack, queue, reference counting</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
     </r>
     <r>
       <rPr>
@@ -1450,12 +1450,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Khi function gọi đệ quy hoặc gọi lại chính nó cần lock</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t xml:space="preserve"> Cấu trúc dữ liệu không dùng lock, dùng atomic operations và CAS.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
     </r>
     <r>
       <rPr>
@@ -1466,7 +1466,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Mutex với khả năng timeout khi chờ lock.</t>
+      <t xml:space="preserve"> High-performance queue, stack, hash table trong hệ thống low-latency</t>
     </r>
   </si>
   <si>
@@ -1482,7 +1482,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Tránh deadlock, có thể bỏ qua nếu không lấy được lock sau một thời gian</t>
+      <t xml:space="preserve"> Truyền kết quả giữa threads, async task management</t>
     </r>
   </si>
   <si>
@@ -1498,12 +1498,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Mutex hỗ trợ shared (read) lock và exclusive (write) lock - Reader-Writer lock.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
+      <t xml:space="preserve"> Hàm tiện ích chạy function async và trả về future.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std::launch::async</t>
     </r>
     <r>
       <rPr>
@@ -1514,12 +1514,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Read-heavy workloads, nhiều reader ít writer</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t>: Chắc chắn tạo thread mới</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std::launch::deferred</t>
     </r>
     <r>
       <rPr>
@@ -1530,12 +1530,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> RAII wrapper cho mutex, tự động unlock khi ra khỏi scope.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ƯU ĐIỂM:</t>
+      <t>: Lazy evaluation, chạy khi gọi get()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
     </r>
     <r>
       <rPr>
@@ -1546,7 +1546,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Exception-safe, đơn giản, không thể quên unlock</t>
+      <t xml:space="preserve"> Thread pool, task queue với kết quả trả về</t>
     </r>
   </si>
   <si>
@@ -1562,7 +1562,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Lock linh hoạt hơn lock_guard, có thể unlock/relock, defer lock, try_lock.</t>
+      <t xml:space="preserve"> Future có thể copy và share giữa nhiều threads (std::future chỉ move-only).</t>
     </r>
   </si>
   <si>
@@ -1578,12 +1578,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Dùng với condition_variable, cần unlock/relock trong scope</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t xml:space="preserve"> Broadcast kết quả cho nhiều threads</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giải pháp:</t>
     </r>
     <r>
       <rPr>
@@ -1594,12 +1594,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Lock cho shared access với shared_mutex.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t xml:space="preserve"> Dùng std::scoped_lock, lock theo thứ tự cố định</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giải pháp:</t>
     </r>
     <r>
       <rPr>
@@ -1610,12 +1610,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Lock nhiều mutex cùng lúc một cách deadlock-free (RAII cho std::lock).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
+      <t xml:space="preserve"> Luôn protect shared data bằng mutex hoặc atomic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giải pháp:</t>
     </r>
     <r>
       <rPr>
@@ -1626,12 +1626,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Tránh deadlock khi cần lock nhiều mutex cùng lúc</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t xml:space="preserve"> Luôn join hoặc detach trong destructor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giải pháp:</t>
     </r>
     <r>
       <rPr>
@@ -1642,12 +1642,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Cơ chế đồng bộ cho phép thread chờ cho đến khi một điều kiện được thỏa mãn.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa wait():</t>
+      <t xml:space="preserve"> Luôn dùng predicate trong wait()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giải pháp:</t>
     </r>
     <r>
       <rPr>
@@ -1658,12 +1658,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Thread chờ cho đến khi được notify và condition được thỏa mãn.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa notify_one():</t>
+      <t xml:space="preserve"> Try-catch trong thread function</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quên dùng </t>
     </r>
     <r>
       <rPr>
@@ -1674,28 +1674,120 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Đánh thức một thread đang chờ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa notify_all():</t>
-    </r>
+      <t>std::ref() khi muốn pass by reference → thread sẽ copy giá trị</t>
+    </r>
+  </si>
+  <si>
+    <t>để tạo và quản lý các luồng thực thi độc lập trong chương trình.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Định nghĩa: std::thread là class chuẩn trong C++11 </t>
+  </si>
+  <si>
+    <t>Trong C++98 không có std::thread</t>
+  </si>
+  <si>
+    <t>Dùng API của hệ điều hành hoặc thư viện ngoài:</t>
+  </si>
+  <si>
+    <t>POSIX Threads (pthread) — Unix/Linux</t>
+  </si>
+  <si>
+    <t>[ ] POSIX Threads (pthread)</t>
+  </si>
+  <si>
+    <t>[ ] Windows Threads — Win32 API</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>[ ]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Thread trong C++ 98</t>
+    </r>
+  </si>
+  <si>
+    <t>#include &lt;pthread.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;iostream&gt;</t>
+  </si>
+  <si>
+    <t>void* run(void* arg) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; "Hello from thread\n";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return nullptr;</t>
+  </si>
+  <si>
+    <t>int main() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    pthread_t t;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    pthread_create(&amp;t, NULL, run, NULL);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    pthread_join(t, NULL);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return 0;</t>
+  </si>
+  <si>
+    <t>Windows Threads</t>
+  </si>
+  <si>
+    <t>#include &lt;windows.h&gt;</t>
+  </si>
+  <si>
+    <t>DWORD WINAPI run(LPVOID) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    HANDLE h = CreateThread(NULL, 0, run, NULL, 0, NULL);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    WaitForSingleObject(h, INFINITE);</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Đánh thức tất cả threads đang chờ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
+      <t xml:space="preserve"> Cách truyền tham số vào hàm thực thi của thread.</t>
+    </r>
+  </si>
+  <si>
+    <t>và swap nếu bằng expected, cơ sở của lock-free algorithms.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
     </r>
     <r>
       <rPr>
@@ -1706,8 +1798,11 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Producer-Consumer pattern, thread pool task queue</t>
-    </r>
+      <t xml:space="preserve"> Instruction đảm bảo thứ tự memory operations, </t>
+    </r>
+  </si>
+  <si>
+    <t>ngăn compiler/CPU reorder instructions.</t>
   </si>
   <si>
     <r>
@@ -1722,12 +1817,15 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Hiện tượng thread bị đánh thức từ wait() mà không có notify() thực sự, hoặc condition chưa thỏa mãn.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>BẪY THƯỜNG GẶP:</t>
+      <t xml:space="preserve"> Vấn đề trong CAS: giá trị A → B → A, </t>
+    </r>
+  </si>
+  <si>
+    <t>CAS nghĩ không đổi nhưng thực ra đã thay đổi và quay lại.</t>
+  </si>
+  <si>
+    <r>
+      <t>LƯU Ý:</t>
     </r>
     <r>
       <rPr>
@@ -1738,12 +1836,15 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Không check condition sau khi wake up → xử lý sai dữ liệu</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ƯU ĐIỂM:</t>
+      <t xml:space="preserve"> Rất khó sử dụng đúng, thường </t>
+    </r>
+  </si>
+  <si>
+    <t>dùng memory ordering trong atomic operations thay vì fence trực tiếp</t>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
     </r>
     <r>
       <rPr>
@@ -1754,8 +1855,17 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Nhanh hơn mutex cho các operation đơn giản, lock-free</t>
-    </r>
+      <t xml:space="preserve"> Tối ưu performance trong lock-free programming, </t>
+    </r>
+  </si>
+  <si>
+    <t>nhưng rất dễ sai nếu không hiểu rõ</t>
+  </si>
+  <si>
+    <t>không thể bị gián đoạn giữa chừng.</t>
+  </si>
+  <si>
+    <t>operation nguyên tử (không thể bị interrupt) trên type T, không cần mutex.</t>
   </si>
   <si>
     <r>
@@ -1770,15 +1880,28 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Quy định thứ tự thực hiện các atomic operations giữa các threads (memory model).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve"> Wrapper cho callable object </t>
+    </r>
+  </si>
+  <si>
+    <t>(function, lambda) kèm theo future để lấy kết quả.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không gọi join() hoặc detach() trước khi thread object bị hủy → std::terminate() </t>
+  </si>
+  <si>
+    <t>Detach rồi main thread kết thúc → thread con có thể bị terminate - kết thúc đột ngột</t>
+  </si>
+  <si>
+    <t>Trong Linux/Windows:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">process kết thúc ⇒ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -1786,12 +1909,15 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Lock-free stack, queue, reference counting</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t>mọi thread bị kill</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong RTOS (FreeRTOS, Zephyr, ThreadX…):</t>
+  </si>
+  <si>
+    <r>
+      <t>main()</t>
     </r>
     <r>
       <rPr>
@@ -1802,15 +1928,11 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Cấu trúc dữ liệu không dùng lock, dùng atomic operations và CAS.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve"> kết thúc ⇒ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -1818,15 +1940,16 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> High-performance queue, stack, hash table trong hệ thống low-latency</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa future:</t>
-    </r>
-    <r>
-      <rPr>
+      <t>process kết thúc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Không có “process”, chỉ có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -1834,12 +1957,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Object đại diện cho giá trị sẽ có trong tương lai, kết quả của async operation.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa promise:</t>
+      <t>task</t>
     </r>
     <r>
       <rPr>
@@ -1850,12 +1968,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Object dùng để set giá trị cho future tương ứng.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>main()</t>
     </r>
     <r>
       <rPr>
@@ -1866,15 +1984,11 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Truyền kết quả giữa threads, async task management</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -1882,12 +1996,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Hàm tiện ích chạy function async và trả về future.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>std::launch::async</t>
+      <t>không phải entrypoint bảo đảm tồn tại suốt runtime</t>
     </r>
     <r>
       <rPr>
@@ -1898,12 +2007,12 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Chắc chắn tạo thread mới</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>std::launch::deferred</t>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sau khi khởi tạo RTOS Scheduler, </t>
     </r>
     <r>
       <rPr>
@@ -1914,15 +2023,11 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Lazy evaluation, chạy khi gọi get()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">main() thường </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -1930,12 +2035,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Thread pool, task queue với kết quả trả về</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
+      <t>kết thúc ngay lập tức</t>
     </r>
     <r>
       <rPr>
@@ -1946,79 +2046,98 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Future có thể copy và share giữa nhiều threads (std::future chỉ move-only).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t>, nhưng hệ thống vẫn chạy.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chú ý :</t>
+  </si>
+  <si>
+    <t>Định nghĩa join(): Chặn thread hiện tại cho đến khi thread được gọi join() hoàn thành.</t>
+  </si>
+  <si>
+    <t>Định nghĩa detach(): Tách thread khỏi thread chính, thread sẽ chạy độc lập, không thể join() sau đó.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::thread t(task);   // tạo thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    t.join();              // chờ thread kết thúc</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Created</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Broadcast kết quả cho nhiều threads</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Giải pháp:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t>: Thread object được tạo, thread bắt đầu thực thi ngay</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Running</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Dùng std::scoped_lock, lock theo thứ tự cố định</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Giải pháp:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t>: Thread đang thực thi task</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Luôn protect shared data bằng mutex hoặc atomic</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Giải pháp:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t>: Task hoàn thành, chờ join() hoặc đã detach()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Joined/Detached</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Luôn join hoặc detach trong destructor</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Giải pháp:</t>
-    </r>
-    <r>
-      <rPr>
+      <t>: Thread được join() hoặc detach()</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi tạo thread:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thread vào </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -2026,15 +2145,16 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Luôn dùng predicate trong wait()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Giải pháp:</t>
-    </r>
-    <r>
-      <rPr>
+      <t>queue READY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Scheduler quyết định </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -2042,12 +2162,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Try-catch trong thread function</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quên dùng </t>
+      <t>ai được chạy trước</t>
     </r>
     <r>
       <rPr>
@@ -2058,97 +2173,8 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t>std::ref() khi muốn pass by reference → thread sẽ copy giá trị</t>
-    </r>
-  </si>
-  <si>
-    <t>để tạo và quản lý các luồng thực thi độc lập trong chương trình.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Định nghĩa: std::thread là class chuẩn trong C++11 </t>
-  </si>
-  <si>
-    <t>Trong C++98 không có std::thread</t>
-  </si>
-  <si>
-    <t>Dùng API của hệ điều hành hoặc thư viện ngoài:</t>
-  </si>
-  <si>
-    <t>POSIX Threads (pthread) — Unix/Linux</t>
-  </si>
-  <si>
-    <t>[ ] POSIX Threads (pthread)</t>
-  </si>
-  <si>
-    <t>[ ] Windows Threads — Win32 API</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-      </rPr>
-      <t>[ ]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-      </rPr>
-      <t xml:space="preserve"> Thread trong C++ 98</t>
-    </r>
-  </si>
-  <si>
-    <t>#include &lt;pthread.h&gt;</t>
-  </si>
-  <si>
-    <t>#include &lt;iostream&gt;</t>
-  </si>
-  <si>
-    <t>void* run(void* arg) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    std::cout &lt;&lt; "Hello from thread\n";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    return nullptr;</t>
-  </si>
-  <si>
-    <t>int main() {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    pthread_t t;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    pthread_create(&amp;t, NULL, run, NULL);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    pthread_join(t, NULL);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    return 0;</t>
-  </si>
-  <si>
-    <t>Windows Threads</t>
-  </si>
-  <si>
-    <t>#include &lt;windows.h&gt;</t>
-  </si>
-  <si>
-    <t>DWORD WINAPI run(LPVOID) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    HANDLE h = CreateThread(NULL, 0, run, NULL, 0, NULL);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    WaitForSingleObject(h, INFINITE);</t>
+      <t xml:space="preserve"> (main hay thread mới)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2163,27 +2189,31 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Cách truyền tham số vào hàm thực thi của thread.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> Namespace chứa các function để thao tác với thread hiện tại.</t>
+    </r>
+  </si>
+  <si>
+    <t>Định nghĩa thread ID: Mỗi thread có một ID duy nhất để phân biệt.</t>
+  </si>
+  <si>
+    <t>Định nghĩa hardware concurrency: Số lượng thread có thể chạy đồng thời trên phần cứng.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        std::cerr &lt;&lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Operation nguyên tử so sánh giá trị </t>
-    </r>
-  </si>
-  <si>
-    <t>và swap nếu bằng expected, cơ sở của lock-free algorithms.</t>
+      <t>e.what(); // in ra "Error in thread"</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2192,17 +2222,347 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Instruction đảm bảo thứ tự memory operations, </t>
-    </r>
-  </si>
-  <si>
-    <t>ngăn compiler/CPU reorder instructions.</t>
+      <t xml:space="preserve"> Cách xử lý exception xảy ra trong thread để tránh terminate.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   lock() nhiều lần liên tiếp -&gt; deadlock</t>
+  </si>
+  <si>
+    <t>Cần unlock đúng số lần đã lock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Chỉ thread cầm lock() mới có quyền ghi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Các thread còn lại cầm lock_share() chỉ có quyền độc. </t>
+  </si>
+  <si>
+    <t>Định nghĩa:</t>
+  </si>
+  <si>
+    <t>Đặc điểm:</t>
+  </si>
+  <si>
+    <t>Dễ lập trình, khó tối ưu hiệu năng khi có các thao tác chậm (I/O, mạng, truy xuất thiết bị).</t>
+  </si>
+  <si>
+    <t>Ví dụ điển hình: Đọc file xong rồi mới xử lý nội dung.</t>
+  </si>
+  <si>
+    <t>Synchronous</t>
+  </si>
+  <si>
+    <t>Một tác vụ đồng bộ yêu cầu chương trình chờ đợi kết quả trước khi chuyển sang thao tác tiếp theo.</t>
+  </si>
+  <si>
+    <t>Các lệnh/thao tác được thực hiện tuần tự, lần lượt.</t>
+  </si>
+  <si>
+    <t>Thread/Process đợi tác vụ hoàn tất mới thực hiện tiếp.</t>
+  </si>
+  <si>
+    <t>Mã giả:</t>
+  </si>
+  <si>
+    <t>result = read_file("data.txt"); // Chờ đọc xong</t>
+  </si>
+  <si>
+    <t>process(result);                // Xử lý sau khi đã có dữ liệu</t>
+  </si>
+  <si>
+    <t>Asynchronous</t>
+  </si>
+  <si>
+    <t>Các thao tác bất đồng bộ được khởi động, nhưng thread/chương trình không chờ đợi kết quả lập tức.</t>
+  </si>
+  <si>
+    <t>Có thể tiếp tục thực hiện công việc khác, khi nào tác vụ hoàn tất sẽ gửi tín hiệu/callback báo cho chương trình.</t>
+  </si>
+  <si>
+    <t>Không chặn thread chính/chương trình khi thao tác chưa hoàn tất.</t>
+  </si>
+  <si>
+    <t>Thường liên quan đến multi-threading, callback, promise/future, event loop.</t>
+  </si>
+  <si>
+    <t>Tốt cho các tác vụ lâu, cần hiệu năng (đọc file lớn, xử lý mạng, tác vụ nền).</t>
+  </si>
+  <si>
+    <t>Cần cơ chế đồng bộ tín hiệu (condition_variable, event, callback) để biết kết quả khi tác vụ kết thúc.</t>
+  </si>
+  <si>
+    <t>async_read_file("data.txt", [](result){</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    process(result); // Được gọi khi đọc file xong (callback)</t>
+  </si>
+  <si>
+    <t>// Chương trình vẫn thực hiện các công việc khác ngay lập tức sau khi gọi async_read_file</t>
+  </si>
+  <si>
+    <t>Định nghĩa Semaphore</t>
+  </si>
+  <si>
+    <t>Định nghĩa</t>
+  </si>
+  <si>
+    <t>#include &lt;semaphore&gt;</t>
+  </si>
+  <si>
+    <t>// Template parameter = giá trị max của counter</t>
+  </si>
+  <si>
+    <t>std::counting_semaphore&lt;5&gt; sem(3);  // Counter khởi tạo = 3, max = 5</t>
+  </si>
+  <si>
+    <t>Các Operations Cơ Bản</t>
+  </si>
+  <si>
+    <t>acquire() - Giảm counter</t>
+  </si>
+  <si>
+    <t>std::counting_semaphore&lt;10&gt; sem(3);  // Counter = 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sem.acquire();  // Counter giảm: 3 -&gt; 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Critical section - tối đa 3 threads vào đồng thời</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sem.release();  // Counter tăng: 2 -&gt; 3</t>
+  </si>
+  <si>
+    <t>// Sử dụng:</t>
+  </si>
+  <si>
+    <t>std::vector&lt;std::thread&gt; threads;</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; 10; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    threads.emplace_back(worker);</t>
+  </si>
+  <si>
+    <t>for (auto&amp; t : threads) t.join();</t>
+  </si>
+  <si>
+    <t>release() - Tăng counter</t>
+  </si>
+  <si>
+    <t>sem.release();     // Tăng 1</t>
+  </si>
+  <si>
+    <t>sem.release(3);    // Tăng 3</t>
+  </si>
+  <si>
+    <t>std::counting_semaphore&lt;5&gt; sem(5);</t>
+  </si>
+  <si>
+    <t>sem.release();  // Counter = 6, vượt quá max!</t>
+  </si>
+  <si>
+    <t>// Undefined behavior nếu counter &gt; max template parameter</t>
+  </si>
+  <si>
+    <t>try_acquire() - Non-blocking acquire</t>
+  </si>
+  <si>
+    <t>if (sem.try_acquire()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Thành công, đã acquire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Critical section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sem.release();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Thất bại, counter = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Xử lý khác</t>
+  </si>
+  <si>
+    <t>try_acquire_for() - Acquire với timeout</t>
+  </si>
+  <si>
+    <t>if (sem.try_acquire_for(std::chrono::milliseconds(100))) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Acquire thành công trong 100ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Timeout sau 100ms</t>
+  </si>
+  <si>
+    <t>try_acquire_until() - Acquire đến thời điểm cụ thể</t>
+  </si>
+  <si>
+    <t>auto deadline = std::chrono::steady_clock::now() + std::chrono::seconds(5);</t>
+  </si>
+  <si>
+    <t>if (sem.try_acquire_until(deadline)) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Acquire thành công trước deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Hết thời gian</t>
+  </si>
+  <si>
+    <t>// Tương đương: std::counting_semaphore&lt;1&gt;</t>
+  </si>
+  <si>
+    <t>std::binary_semaphore sem(1);  // Counter = 0 hoặc 1</t>
+  </si>
+  <si>
+    <t>// Khởi tạo:</t>
+  </si>
+  <si>
+    <t>std::binary_semaphore sem_locked(0);    // Bắt đầu locked</t>
+  </si>
+  <si>
+    <t>std::binary_semaphore sem_unlocked(1);  // Bắt đầu unlocked</t>
+  </si>
+  <si>
+    <t>So sánh Binary Semaphore vs Mutex</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>std::binary_semaphore</t>
+  </si>
+  <si>
+    <t>Ownership</t>
+  </si>
+  <si>
+    <t>KHÔNG có</t>
+  </si>
+  <si>
+    <t>CÓ (thread lock phải unlock)</t>
+  </si>
+  <si>
+    <t>Release từ thread khác</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>KHÔNG được</t>
+  </si>
+  <si>
+    <t>Recursive locking</t>
+  </si>
+  <si>
+    <t>KHÔNG</t>
+  </si>
+  <si>
+    <t>Cần std::recursive_mutex</t>
+  </si>
+  <si>
+    <t>Signaling giữa threads</t>
+  </si>
+  <si>
+    <t>TỐT</t>
+  </si>
+  <si>
+    <t>KHÔNG phù hợp</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Tương tự</t>
+  </si>
+  <si>
+    <t>// Binary semaphore - release từ thread khác OK:</t>
+  </si>
+  <si>
+    <t>std::binary_semaphore sem(0);</t>
+  </si>
+  <si>
+    <t>void producer() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Produce data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sem.release();  // Signal consumer</t>
+  </si>
+  <si>
+    <t>void consumer() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sem.acquire();  // Chờ producer signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Consume data</t>
+  </si>
+  <si>
+    <t>// Mutex - KHÔNG thể làm như vậy:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    mtx.lock();    // Lock ở đây</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    mtx.unlock();  // UNDEFINED BEHAVIOR! Consumer không own mutex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t>sem.acquire();</t>
+  </si>
+  <si>
+    <t>Trước C++20 (POSIX semaphore)</t>
+  </si>
+  <si>
+    <t>#include &lt;semaphore.h&gt;  // POSIX</t>
+  </si>
+  <si>
+    <t>sem_t sem;</t>
+  </si>
+  <si>
+    <t>sem_init(&amp;sem, 0, 3);   // Initialize với count = 3</t>
+  </si>
+  <si>
+    <t>sem_wait(&amp;sem);         // acquire()</t>
+  </si>
+  <si>
+    <t>// Critical section</t>
+  </si>
+  <si>
+    <t>sem_post(&amp;sem);         // release()</t>
+  </si>
+  <si>
+    <t>sem_destroy(&amp;sem);</t>
+  </si>
+  <si>
+    <t>C++20 std::semaphore</t>
+  </si>
+  <si>
+    <t>#include &lt;semaphore&gt;    // C++ Standard</t>
+  </si>
+  <si>
+    <t>std::counting_semaphore&lt;10&gt; sem(3);  // Type-safe, RAII-friendly</t>
+  </si>
+  <si>
+    <t>sem.release();</t>
+  </si>
+  <si>
+    <t>// Tự động cleanup khi out of scope</t>
   </si>
   <si>
     <r>
@@ -2211,55 +2571,615 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mutex cho phép cùng một thread lock nhiều lần (reentrant).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mutex với khả năng timeout khi chờ lock.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Khi function gọi đệ quy hoặc gọi lại chính nó cần lock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mutex hỗ trợ shared (read) lock và exclusive (write) lock - Reader-Writer lock.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Read-heavy workloads, nhiều reader ít writer</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tránh deadlock khi cần lock nhiều mutex cùng lúc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BẪY THƯỜNG GẶP:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Không check condition sau khi wake up → xử lý sai dữ liệu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Producer-Consumer pattern, thread pool task queue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VẤN ĐỀ:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Platform-specific, không portable, không RAII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ƯU ĐIỂM:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Portable, type-safe, modern C++ idioms</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mutual Exclusion object, đảm bảo </t>
+    </r>
+  </si>
+  <si>
+    <t>chỉ một thread truy cập critical section tại một thời điểm.</t>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tránh deadlock, có thể bỏ qua nếu </t>
+    </r>
+  </si>
+  <si>
+    <t>không lấy được lock sau một thời gian</t>
+  </si>
+  <si>
+    <t>tự động unlock khi ra khỏi scope.</t>
+  </si>
+  <si>
+    <r>
+      <t>ƯU ĐIỂM:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Exception-safe, đơn giản, không thể quên unlock</t>
+  </si>
+  <si>
+    <t>có thể unlock/relock, defer lock, try_lock.</t>
+  </si>
+  <si>
+    <r>
+      <t>ỨNG DỤNG:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dùng với condition_variable, </t>
+    </r>
+  </si>
+  <si>
+    <t>cần unlock/relock trong scope</t>
+  </si>
+  <si>
+    <t>Semaphore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiểm soát số lượng threads có thể truy cập vào một resource hoặc critical section đồng thời. </t>
+  </si>
+  <si>
+    <t>Khác với mutex (chỉ cho 1 thread), semaphore cho phép N threads cùng truy cập.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>[ ] std::counting_semaphore&lt;N&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ ] std::binary_semaphore   </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Semaphore   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> RAII wrapper cho mutex, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Lock linh hoạt hơn lock_guard, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Lock cho shared access với shared_mutex.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Lock nhiều mutex cùng lúc một cách deadlock-free (RAII cho std::lock).</t>
+    </r>
+  </si>
+  <si>
+    <t>cho phép thread chờ cho đến khi một điều kiện được thỏa mãn.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cơ chế đồng bộ </t>
+    </r>
+  </si>
+  <si>
+    <t>mà không có notify() thực sự, hoặc condition chưa thỏa mãn.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa wait():</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thread chờ cho đến khi được notify và condition được thỏa mãn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa notify_one():</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Đánh thức một thread đang chờ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa notify_all():</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Đánh thức tất cả threads đang chờ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Hiện tượng thread bị đánh thức từ wait() </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Semaphore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là một synchronization primitive dùng để </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C++ Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Semaphore được giới thiệu chính thức trong </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C++20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> qua header &lt;semaphore&gt;.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std::counting_semaphore&lt;N&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là semaphore với counter có thể đếm từ 0 đến N, </t>
+    </r>
+  </si>
+  <si>
+    <t>cho phép tối đa N threads acquire cùng lúc.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Giảm counter đi 1, block nếu counter = 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tăng counter đi 1 hoặc nhiều hơn, đánh thức threads đang chờ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thử giảm counter, return ngay lập tức (không block).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thử acquire trong một khoảng thời gian, timeout nếu không được.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thử acquire cho đến một timepoint.</t>
+    </r>
+  </si>
+  <si>
+    <t>COUNTING SEMAPHORE (std::counting_semaphore)</t>
+  </si>
+  <si>
+    <t>BINARY SEMAPHORE (std::binary_semaphore)</t>
+  </si>
+  <si>
+    <t>tương tự mutex nhưng không có ownership concept.</t>
+  </si>
+  <si>
+    <r>
+      <t>std::binary_semaphore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là alias của counting_semaphore với max = 1, </t>
+    </r>
+  </si>
+  <si>
+    <t>[ ] example</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Asynchronous</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Synchronous</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Vấn đề trong CAS: giá trị A → B → A, </t>
-    </r>
-  </si>
-  <si>
-    <t>CAS nghĩ không đổi nhưng thực ra đã thay đổi và quay lại.</t>
-  </si>
-  <si>
-    <r>
-      <t>LƯU Ý:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> Template class cung cấp các </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Rất khó sử dụng đúng, thường </t>
-    </r>
-  </si>
-  <si>
-    <t>dùng memory ordering trong atomic operations thay vì fence trực tiếp</t>
-  </si>
-  <si>
-    <r>
-      <t>ỨNG DỤNG:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> Các phép toán được thực hiện nguyên tử, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Tối ưu performance trong lock-free programming, </t>
-    </r>
-  </si>
-  <si>
-    <t>nhưng rất dễ sai nếu không hiểu rõ</t>
+      <t xml:space="preserve"> Quy định thứ tự thực hiện các atomic operations giữa các threads (memory model).</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2268,68 +3188,50 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Các phép toán được thực hiện nguyên tử, </t>
-    </r>
-  </si>
-  <si>
-    <t>không thể bị gián đoạn giữa chừng.</t>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> Operation nguyên tử so sánh giá trị </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa future:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Template class cung cấp các </t>
-    </r>
-  </si>
-  <si>
-    <t>operation nguyên tử (không thể bị interrupt) trên type T, không cần mutex.</t>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> Object đại diện cho giá trị sẽ có trong tương lai, kết quả của async operation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa promise:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Wrapper cho callable object </t>
-    </r>
-  </si>
-  <si>
-    <t>(function, lambda) kèm theo future để lấy kết quả.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không gọi join() hoặc detach() trước khi thread object bị hủy → std::terminate() </t>
-  </si>
-  <si>
-    <t>Detach rồi main thread kết thúc → thread con có thể bị terminate - kết thúc đột ngột</t>
-  </si>
-  <si>
-    <t>Trong Linux/Windows:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">process kết thúc ⇒ </t>
+      <t xml:space="preserve"> Object dùng để set giá trị cho future tương ứng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
     </r>
     <r>
       <rPr>
@@ -2338,337 +3240,235 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>mọi thread bị kill</t>
-    </r>
-  </si>
-  <si>
-    <t>Trong RTOS (FreeRTOS, Zephyr, ThreadX…):</t>
-  </si>
-  <si>
-    <r>
-      <t>main()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> kết thúc ⇒ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>process kết thúc</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Không có “process”, chỉ có </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>task</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>main()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>không phải entrypoint bảo đảm tồn tại suốt runtime</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sau khi khởi tạo RTOS Scheduler, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">main() thường </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>kết thúc ngay lập tức</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, nhưng hệ thống vẫn chạy.</t>
-    </r>
-  </si>
-  <si>
-    <t>Chú ý :</t>
-  </si>
-  <si>
-    <t>Định nghĩa join(): Chặn thread hiện tại cho đến khi thread được gọi join() hoàn thành.</t>
-  </si>
-  <si>
-    <t>Định nghĩa detach(): Tách thread khỏi thread chính, thread sẽ chạy độc lập, không thể join() sau đó.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    std::thread t(task);   // tạo thread</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    t.join();              // chờ thread kết thúc</t>
-  </si>
-  <si>
-    <r>
-      <t>1. Created</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Thread object được tạo, thread bắt đầu thực thi ngay</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. Running</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Thread đang thực thi task</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Task hoàn thành, chờ join() hoặc đã detach()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4. Joined/Detached</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Thread được join() hoặc detach()</t>
-    </r>
-  </si>
-  <si>
-    <t>Khi tạo thread:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Thread vào </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>queue READY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Scheduler quyết định </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ai được chạy trước</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (main hay thread mới)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Namespace chứa các function để thao tác với thread hiện tại.</t>
-    </r>
-  </si>
-  <si>
-    <t>Định nghĩa thread ID: Mỗi thread có một ID duy nhất để phân biệt.</t>
-  </si>
-  <si>
-    <t>Định nghĩa hardware concurrency: Số lượng thread có thể chạy đồng thời trên phần cứng.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">        std::cerr &lt;&lt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>e.what(); // in ra "Error in thread"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cách xử lý exception xảy ra trong thread để tránh terminate.</t>
-    </r>
+      </rPr>
+      <t>PSEUDO CODE VxWorks PATTERN</t>
+    </r>
+  </si>
+  <si>
+    <t>PSEUDO CODE VxWorks PATTERN</t>
+  </si>
+  <si>
+    <t>// ============ VxWorks Semaphore APIs ============</t>
+  </si>
+  <si>
+    <t>SEM_ID semBCreate(int options, SEM_B_STATE initialState);</t>
+  </si>
+  <si>
+    <t>STATUS semGive(SEM_ID semId);</t>
+  </si>
+  <si>
+    <t>STATUS semTake(SEM_ID semId, int timeout);</t>
+  </si>
+  <si>
+    <t>// ============ Global Variables ============</t>
+  </si>
+  <si>
+    <t>SEM_ID g_semaphore;           // Binary semaphore</t>
+  </si>
+  <si>
+    <t>int g_commandType;            // Shared: command type</t>
+  </si>
+  <si>
+    <t>void* g_commandData;          // Shared: command data</t>
+  </si>
+  <si>
+    <t>// Command types</t>
+  </si>
+  <si>
+    <t>#define CMD_INTERFACE  1</t>
+  </si>
+  <si>
+    <t>#define CMD_PORT       2</t>
+  </si>
+  <si>
+    <t>#define CMD_COMPUTE    3</t>
+  </si>
+  <si>
+    <t>// ============ Thread Interface (Producer) ============</t>
+  </si>
+  <si>
+    <t>void threadInterface(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    while (1) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (1) Nhận command từ upper layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Data* data = receiveFromUpperLayer();  // Blocking receive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (2) Encode command vào global shared memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        g_commandType = CMD_INTERFACE;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        g_commandData = encodeInterfaceData(data);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (3) Signal thread Execute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        semGive(g_semaphore);  // Wake up consumer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (4) Continue loop - không chờ kết quả</t>
+  </si>
+  <si>
+    <t>// ============ Thread Port (Producer) ============</t>
+  </si>
+  <si>
+    <t>void threadPort(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (1) Nhận report từ hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Report* report = receiveFromHardware();  // Blocking receive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (2) Encode report vào global shared memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        g_commandType = CMD_PORT;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        g_commandData = encodePortData(report);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (4) Continue loop</t>
+  </si>
+  <si>
+    <t>// ============ Thread Execute (Consumer) ============</t>
+  </si>
+  <si>
+    <t>void threadExecute(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (1) Block chờ signal từ producers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        semTake(g_semaphore, WAIT_FOREVER);  // Sleep here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (2) Wake up! Đọc command từ shared memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        int cmdType = g_commandType;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        void* cmdData = g_commandData;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (3) Xử lý theo command type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        switch (cmdType) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            case CMD_INTERFACE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                handleInterfaceCommand(cmdData);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                break;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            case CMD_PORT:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                handlePortReport(cmdData);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            case CMD_COMPUTE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                handleComputeTask(cmdData);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            default:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                // Error handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // (4) Hoàn thành, loop lại và block tại semTake()</t>
+  </si>
+  <si>
+    <t>// ============ Thread Compute (Consumer) ============</t>
+  </si>
+  <si>
+    <t>void threadCompute(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Tương tự threadExecute, hoặc chung 1 semaphore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Tùy thiết kế: có thể dùng chung hoặc riêng semaphore</t>
+  </si>
+  <si>
+    <t>// ============ Main Initialization ============</t>
+  </si>
+  <si>
+    <t>void main(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // (1) Tạo binary semaphore, initial state = EMPTY (0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    g_semaphore = semBCreate(SEM_Q_FIFO, SEM_EMPTY);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // (2) Spawn threads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    taskSpawn("tInterface", 100, 0, 10000, threadInterface, 0,0,0,0,0,0,0,0,0,0);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    taskSpawn("tPort",      100, 0, 10000, threadPort,      0,0,0,0,0,0,0,0,0,0);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    taskSpawn("tExecute",   100, 0, 10000, threadExecute,   0,0,0,0,0,0,0,0,0,0);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    taskSpawn("tCompute",   100, 0, 10000, threadCompute,   0,0,0,0,0,0,0,0,0,0);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // (3) System running...</t>
+  </si>
+  <si>
+    <t>```</t>
+  </si>
+  <si>
+    <t>- **VxWorks** (Wind River)</t>
+  </si>
+  <si>
+    <t>- **FreeRTOS**</t>
+  </si>
+  <si>
+    <t>- **ThreadX**</t>
+  </si>
+  <si>
+    <t>- **QNX**</t>
+  </si>
+  <si>
+    <t>- **RTEMS**</t>
+  </si>
+  <si>
+    <t>**Embedded Systems / RTOS**</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2692,14 +3492,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -2739,6 +3531,32 @@
       <family val="2"/>
       <charset val="163"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2772,7 +3590,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2804,11 +3622,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2844,8 +3677,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2856,21 +3689,87 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3258,18 +4157,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV18"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AV27"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3283,161 +4182,200 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>20</v>
+        <v>654</v>
       </c>
       <c r="AG3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="AV3" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="R4" s="4"/>
       <c r="AG4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AV4" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>22</v>
+        <v>433</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="AG5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AV5" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AV5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="R6" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="AV6" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AV7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R8" s="3"/>
+      <c r="R8" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="AG8" s="3"/>
-    </row>
-    <row r="9" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="AV8" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>25</v>
+      <c r="R9" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AV9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="R10" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="R10" s="3"/>
       <c r="AG10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="R11" s="4" t="s">
-        <v>27</v>
+      <c r="R11" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AG11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="R12" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG12" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="R14" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="R15" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="R17" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="17:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R18" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="18:18" x14ac:dyDescent="0.2">
-      <c r="R17" s="4" t="s">
+    <row r="19" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="R19" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="18:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R18" s="4" t="s">
+    <row r="20" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q20" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="R20" s="4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="R22" s="3" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="23" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="S23" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="24" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="S24" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="26" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="R26" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="27" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="S27" s="2" t="s">
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -3448,19 +4386,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF92"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="18" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -3491,9 +4429,9 @@
       <c r="AX2" s="20"/>
       <c r="AY2" s="20"/>
     </row>
-    <row r="3" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="V3" s="22" t="s">
         <v>44</v>
@@ -3506,12 +4444,12 @@
       <c r="AB3" s="21"/>
       <c r="AC3" s="21"/>
       <c r="AQ3" s="15" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -3525,23 +4463,23 @@
       <c r="K4" s="26"/>
       <c r="L4" s="26"/>
       <c r="V4" s="15" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="V5" s="22" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="AQ5" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>45</v>
@@ -3550,7 +4488,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V7" s="11" t="s">
         <v>46</v>
       </c>
@@ -3558,16 +4496,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="V8" s="11"/>
       <c r="AQ8" s="11"/>
     </row>
-    <row r="9" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="V9" s="16" t="s">
         <v>47</v>
@@ -3577,9 +4515,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="V10" s="16" t="s">
         <v>48</v>
@@ -3589,7 +4527,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>50</v>
       </c>
@@ -3599,7 +4537,7 @@
       <c r="W11" s="21"/>
       <c r="AQ11" s="11"/>
     </row>
-    <row r="12" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V12" s="16" t="s">
         <v>50</v>
       </c>
@@ -3608,9 +4546,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="V13" s="16" t="s">
         <v>51</v>
@@ -3620,18 +4558,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="V14" s="11"/>
       <c r="AQ14" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="V15" s="22" t="s">
         <v>52</v>
@@ -3640,18 +4578,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="V16" s="22" t="s">
         <v>53</v>
       </c>
       <c r="AQ16" s="11"/>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="V17" s="11" t="s">
         <v>49</v>
@@ -3660,7 +4598,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>50</v>
       </c>
@@ -3671,15 +4609,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="V19" s="11"/>
       <c r="AQ19" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
@@ -3693,17 +4631,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="V21" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="V22" s="16" t="s">
         <v>57</v>
@@ -3712,17 +4650,17 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="V23" s="16" t="s">
         <v>58</v>
       </c>
       <c r="AQ23" s="12" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="V24" s="16" t="s">
         <v>59</v>
@@ -3731,23 +4669,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="V25" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="V26" s="16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>50</v>
       </c>
@@ -3755,51 +4693,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="V28" s="11"/>
     </row>
-    <row r="29" spans="1:43" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="V29" s="22" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:43" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="V30" s="11" t="s">
         <v>64</v>
       </c>
       <c r="AQ30" s="14" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="31" spans="1:43" ht="15" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="V31" s="11" t="s">
         <v>57</v>
       </c>
       <c r="AQ31" s="12" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="32" spans="1:43" ht="15" x14ac:dyDescent="0.2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="V32" s="11" t="s">
         <v>65</v>
       </c>
       <c r="AQ32" s="12" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="33" spans="1:58" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="33" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>50</v>
       </c>
@@ -3808,17 +4746,17 @@
       </c>
       <c r="AQ33" s="12"/>
     </row>
-    <row r="34" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.25">
       <c r="V34" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.25">
       <c r="V35" s="22" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>83</v>
       </c>
@@ -3843,9 +4781,9 @@
       <c r="BE37" s="20"/>
       <c r="BF37" s="20"/>
     </row>
-    <row r="38" spans="1:58" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="AE38" s="7" t="s">
         <v>407</v>
@@ -3854,82 +4792,82 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:58" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="AE39" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AZ39" s="15" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="40" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="40" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>84</v>
       </c>
       <c r="AE40" s="28" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="AF40" s="21"/>
       <c r="AZ40" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="AE41" s="28" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="AF41" s="21"/>
       <c r="AZ41" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>85</v>
       </c>
       <c r="AE42" s="28" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="AF42" s="21"/>
       <c r="AZ42" s="11"/>
     </row>
-    <row r="43" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
         <v>86</v>
       </c>
       <c r="AE43" s="28" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="AF43" s="21"/>
       <c r="AZ43" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="10" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="AZ44" s="11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B45" s="10" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="AE45" s="11" t="s">
         <v>95</v>
       </c>
       <c r="AZ45" s="11"/>
     </row>
-    <row r="46" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B46" s="10" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="AE46" s="11" t="s">
         <v>96</v>
@@ -3938,9 +4876,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B47" s="10" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="AE47" s="11" t="s">
         <v>50</v>
@@ -3949,14 +4887,14 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B48" s="10" t="s">
         <v>50</v>
       </c>
       <c r="AE48" s="11"/>
       <c r="AZ48" s="11"/>
     </row>
-    <row r="49" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
         <v>87</v>
       </c>
@@ -3967,7 +4905,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
         <v>88</v>
       </c>
@@ -3978,7 +4916,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="AE51" s="11" t="s">
         <v>99</v>
@@ -3987,7 +4925,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
         <v>89</v>
       </c>
@@ -3996,12 +4934,12 @@
       </c>
       <c r="AZ52" s="11"/>
     </row>
-    <row r="53" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>90</v>
       </c>
       <c r="AD53" s="25" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="AE53" s="26"/>
       <c r="AF53" s="26"/>
@@ -4009,64 +4947,64 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>91</v>
       </c>
       <c r="AE54" s="15" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="AZ54" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>50</v>
       </c>
       <c r="AE55" s="12" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="56" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="AE56" s="12" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="57" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>81</v>
       </c>
       <c r="AE57" s="15" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="58" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A58" s="27" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="AE58" s="12" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="59" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>92</v>
       </c>
       <c r="AE59" s="12" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="60" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="AE60" s="12" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="62" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>113</v>
       </c>
@@ -4092,29 +5030,29 @@
       <c r="AK62" s="20"/>
       <c r="AL62" s="20"/>
     </row>
-    <row r="63" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="AD63" s="15" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="64" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="AD64" s="11" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
         <v>114</v>
       </c>
       <c r="AD65" s="11"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>84</v>
       </c>
@@ -4122,7 +5060,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>115</v>
       </c>
@@ -4130,13 +5068,13 @@
         <v>125</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
       <c r="AD68" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>116</v>
       </c>
@@ -4144,7 +5082,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>117</v>
       </c>
@@ -4152,7 +5090,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>118</v>
       </c>
@@ -4160,21 +5098,21 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:30" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>50</v>
       </c>
       <c r="AD72" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="11"/>
       <c r="AD73" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
         <v>119</v>
       </c>
@@ -4182,13 +5120,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>120</v>
       </c>
       <c r="AD75" s="11"/>
     </row>
-    <row r="76" spans="1:30" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>121</v>
       </c>
@@ -4196,83 +5134,83 @@
         <v>130</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="AD77" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="1:30" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>408</v>
       </c>
       <c r="AD78" s="11"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="AD79" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="AD80" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="81" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD81" s="16" t="s">
         <v>132</v>
       </c>
       <c r="AE81" s="21"/>
     </row>
-    <row r="82" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD82" s="11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="83" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="83" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD83" s="16" t="s">
         <v>134</v>
       </c>
       <c r="AE83" s="21"/>
     </row>
-    <row r="84" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD84" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="85" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD85" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="86" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD86" s="11"/>
     </row>
-    <row r="87" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="87" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD87" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="88" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD88" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="89" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="89" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD89" s="16" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="90" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD90" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="91" spans="30:31" x14ac:dyDescent="0.2">
+    <row r="91" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD91" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="30:31" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="30:31" x14ac:dyDescent="0.25">
       <c r="AD92" s="7" t="s">
         <v>409</v>
       </c>
@@ -4286,784 +5224,2117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AZ451"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BN243"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="45"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:5" s="40" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:52" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
+        <v>498</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+    </row>
+    <row r="3" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34"/>
+    </row>
+    <row r="7" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="T17" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="AZ2" s="14" t="s">
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="53"/>
+      <c r="Z17" s="53"/>
+      <c r="AP17" s="52" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="3" spans="1:52" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="AQ17" s="53"/>
+      <c r="AR17" s="53"/>
+      <c r="AS17" s="53"/>
+      <c r="AT17" s="53"/>
+      <c r="AU17" s="53"/>
+      <c r="BG17" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="BH17" s="53"/>
+      <c r="BI17" s="53"/>
+      <c r="BJ17" s="53"/>
+      <c r="BK17" s="53"/>
+      <c r="BL17" s="53"/>
+      <c r="BM17" s="53"/>
+      <c r="BN17" s="53"/>
+    </row>
+    <row r="18" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>611</v>
+      </c>
+      <c r="T18" s="31" t="s">
+        <v>601</v>
+      </c>
+      <c r="AP18" s="31" t="s">
+        <v>602</v>
+      </c>
+      <c r="BG18" s="31" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="19" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="54" t="s">
+        <v>612</v>
+      </c>
+      <c r="T19" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="AP19" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG19" s="48" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="T20" s="48"/>
+      <c r="AP20" s="48"/>
+      <c r="BG20" s="48" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="T21" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="AP21" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="BG21" s="48" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="T22" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="AP22" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="BG22" s="48"/>
+    </row>
+    <row r="23" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="48"/>
+      <c r="T23" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP23" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="BG23" s="48" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="T24" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP24" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="BG24" s="48" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="T25" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP25" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="BG25" s="48" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="T26" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="AP26" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="BG26" s="48" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="T27" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP27" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="BG27" s="48" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP28" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="BG28" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T29" s="49" t="s">
+        <v>603</v>
+      </c>
+      <c r="AP29" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="BG29" s="48"/>
+    </row>
+    <row r="30" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="T30" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="BG30" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="AP31" s="49" t="s">
+        <v>613</v>
+      </c>
+      <c r="BG31" s="48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP32" s="45" t="s">
+        <v>614</v>
+      </c>
+      <c r="BG32" s="48" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="BG33" s="48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="31"/>
+      <c r="BG34" s="48" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="31"/>
+      <c r="BG35" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="31"/>
+      <c r="BG36" s="49" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="37" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="31"/>
+      <c r="BG37" s="33" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="38" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="31"/>
+      <c r="BG38" s="33" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="39" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="31"/>
+    </row>
+    <row r="40" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+    </row>
+    <row r="41" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="P41" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q41" s="53"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="53"/>
+      <c r="T41" s="53"/>
+      <c r="AH41" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI41" s="53"/>
+      <c r="AJ41" s="53"/>
+      <c r="AK41" s="53"/>
+      <c r="AL41" s="53"/>
+      <c r="AM41" s="53"/>
+      <c r="AN41" s="53"/>
+      <c r="AO41" s="53"/>
+      <c r="BA41" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="BB41" s="53"/>
+      <c r="BC41" s="53"/>
+      <c r="BD41" s="53"/>
+      <c r="BE41" s="53"/>
+      <c r="BF41" s="53"/>
+      <c r="BG41" s="53"/>
+      <c r="BH41" s="53"/>
+    </row>
+    <row r="42" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="P42" s="31" t="s">
+        <v>629</v>
+      </c>
+      <c r="AH42" s="31" t="s">
+        <v>630</v>
+      </c>
+      <c r="BA42" s="31" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="43" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="54" t="s">
+        <v>615</v>
+      </c>
+      <c r="P43" s="54" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="44" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH44" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="BA44" s="48" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="48"/>
+      <c r="P45" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH45" s="48"/>
+      <c r="BA45" s="48"/>
+    </row>
+    <row r="46" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="P46" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="AH46" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="BA46" s="48" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="P47" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="AH47" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="BA47" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="BB47" s="54"/>
+    </row>
+    <row r="48" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="P48" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH48" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="BA48" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="BB48" s="54"/>
+    </row>
+    <row r="49" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="P49" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="AH49" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="BA49" s="48" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="P50" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH50" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="BA50" s="48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="P51" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="AH51" s="48"/>
+      <c r="BA51" s="48"/>
+    </row>
+    <row r="52" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P52" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="AH52" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="BA52" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="BB52" s="54"/>
+    </row>
+    <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="49" t="s">
+        <v>616</v>
+      </c>
+      <c r="P53" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH53" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="BA53" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="BB53" s="54"/>
+    </row>
+    <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
+        <v>617</v>
+      </c>
+      <c r="P54" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH54" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="BA54" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="BB54" s="54"/>
+    </row>
+    <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P55" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="AH55" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="BA55" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="BB55" s="54"/>
+    </row>
+    <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P56" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH56" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA56" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="BB56" s="54"/>
+    </row>
+    <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P57" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="BA57" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="BB57" s="54"/>
+    </row>
+    <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P58" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BA59" s="49" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P60" s="49" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P61" s="45" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="47"/>
+      <c r="C63" s="47"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="47"/>
+    </row>
+    <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="B64" s="53"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="V64" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="W64" s="53"/>
+      <c r="X64" s="53"/>
+      <c r="Y64" s="53"/>
+      <c r="Z64" s="53"/>
+      <c r="AA64" s="53"/>
+      <c r="AB64" s="53"/>
+      <c r="AC64" s="53"/>
+      <c r="AD64" s="53"/>
+      <c r="AE64" s="53"/>
+      <c r="AW64" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="AX64" s="53"/>
+      <c r="AY64" s="53"/>
+      <c r="AZ64" s="53"/>
+      <c r="BA64" s="53"/>
+      <c r="BB64" s="53"/>
+    </row>
+    <row r="65" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="31" t="s">
+        <v>633</v>
+      </c>
+      <c r="V65" s="31" t="s">
+        <v>635</v>
+      </c>
+      <c r="AW65" s="31" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="66" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="54" t="s">
+        <v>632</v>
+      </c>
+      <c r="V66" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="AW66" s="54" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="67" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="V67" s="31" t="s">
+        <v>637</v>
+      </c>
+      <c r="AW67" s="48" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="48"/>
+      <c r="AW68" s="48" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="69" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="V69" s="48" t="s">
+        <v>225</v>
+      </c>
+      <c r="AW69" s="48"/>
+    </row>
+    <row r="70" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="48" t="s">
+        <v>225</v>
+      </c>
+      <c r="V70" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="AW70" s="48" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="V71" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="AW71" s="48" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="72" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="48"/>
+      <c r="V72" s="48"/>
+      <c r="AW72" s="48"/>
+    </row>
+    <row r="73" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="V73" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="AW73" s="48" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="74" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="V74" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="AW74" s="48" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="75" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="V75" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW75" s="48" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="76" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="48" t="s">
+        <v>229</v>
+      </c>
+      <c r="V76" s="48" t="s">
+        <v>232</v>
+      </c>
+      <c r="AW76" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="V77" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="W77" s="54"/>
+    </row>
+    <row r="78" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="48"/>
+      <c r="V78" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="AW78" s="49" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="79" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="V79" s="48" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="V80" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="B81" s="31"/>
+      <c r="V81" s="48"/>
+    </row>
+    <row r="82" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="B82" s="31"/>
+      <c r="V82" s="48" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="V83" s="48" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="V84" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="V85" s="33" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V86" s="48" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V87" s="48" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V88" s="48" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V89" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V91" s="49" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="32"/>
+    </row>
+    <row r="95" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="32"/>
+    </row>
+    <row r="96" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="56" t="s">
+        <v>621</v>
+      </c>
+      <c r="B96" s="47"/>
+      <c r="C96" s="47"/>
+      <c r="D96" s="47"/>
+    </row>
+    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="32" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="31" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="54" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="54" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="52" t="s">
+        <v>648</v>
+      </c>
+      <c r="B103" s="53"/>
+      <c r="C103" s="53"/>
+      <c r="D103" s="53"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="53"/>
+      <c r="I103" s="53"/>
+      <c r="J103" s="53"/>
+      <c r="K103" s="53"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="53"/>
+      <c r="N103" s="53"/>
+      <c r="O103" s="53"/>
+      <c r="P103" s="53"/>
+      <c r="Q103" s="53"/>
+    </row>
+    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="32" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="49" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="45" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="48" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="48" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="32" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="113" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="R113" s="33" t="s">
+        <v>531</v>
+      </c>
+      <c r="AO113" s="33" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="114" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>643</v>
+      </c>
+      <c r="R114" s="31" t="s">
+        <v>644</v>
+      </c>
+      <c r="AO114" s="31" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="115" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="R115" s="48" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="116" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="48"/>
+      <c r="R116" s="48" t="s">
+        <v>533</v>
+      </c>
+      <c r="AO116" s="48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="117" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="AO117" s="48"/>
+    </row>
+    <row r="118" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="55" t="s">
+        <v>523</v>
+      </c>
+      <c r="R118" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO118" s="48" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="119" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="48" t="s">
+        <v>524</v>
+      </c>
+      <c r="R119" s="48" t="s">
+        <v>534</v>
+      </c>
+      <c r="AO119" s="48" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="120" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="R120" s="55" t="s">
+        <v>535</v>
+      </c>
+      <c r="AO120" s="48" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="121" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="55" t="s">
+        <v>525</v>
+      </c>
+      <c r="R121" s="55" t="s">
+        <v>536</v>
+      </c>
+      <c r="AO121" s="48" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="122" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO122" s="48" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="123" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="48"/>
+      <c r="R123" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="AO123" s="48" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="124" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="48" t="s">
+        <v>526</v>
+      </c>
+      <c r="R124" s="31" t="s">
+        <v>645</v>
+      </c>
+      <c r="AO124" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="48" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="126" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="48" t="s">
+        <v>528</v>
+      </c>
+      <c r="R126" s="48" t="s">
+        <v>538</v>
+      </c>
+      <c r="AO126" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="127" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="48" t="s">
+        <v>529</v>
+      </c>
+      <c r="R127" s="48" t="s">
+        <v>539</v>
+      </c>
+      <c r="AO127" s="31" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="128" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="R128" s="48" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="129" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="48" t="s">
+        <v>530</v>
+      </c>
+      <c r="R129" s="48" t="s">
+        <v>541</v>
+      </c>
+      <c r="AO129" s="48" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="130" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R130" s="48" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO130" s="48"/>
+    </row>
+    <row r="131" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R131" s="48" t="s">
+        <v>542</v>
+      </c>
+      <c r="AO131" s="48" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="132" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R132" s="48" t="s">
+        <v>543</v>
+      </c>
+      <c r="AO132" s="48" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="133" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R133" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO133" s="48" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="134" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO134" s="48" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="135" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO135" s="48" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="136" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO136" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="52" t="s">
+        <v>649</v>
+      </c>
+      <c r="B137" s="53"/>
+      <c r="C137" s="53"/>
+      <c r="D137" s="53"/>
+      <c r="E137" s="53"/>
+      <c r="F137" s="53"/>
+      <c r="G137" s="53"/>
+      <c r="H137" s="53"/>
+      <c r="I137" s="53"/>
+      <c r="J137" s="53"/>
+      <c r="K137" s="53"/>
+      <c r="L137" s="53"/>
+      <c r="M137" s="53"/>
+      <c r="N137" s="53"/>
+    </row>
+    <row r="138" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="Z138" s="32" t="s">
+        <v>558</v>
+      </c>
+      <c r="AZ138" s="48" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="139" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="31" t="s">
+        <v>651</v>
+      </c>
+      <c r="AA139" s="59" t="s">
+        <v>559</v>
+      </c>
+      <c r="AB139" s="59"/>
+      <c r="AC139" s="59"/>
+      <c r="AD139" s="59"/>
+      <c r="AE139" s="59"/>
+      <c r="AF139" s="59"/>
+      <c r="AG139" s="59"/>
+      <c r="AH139" s="59" t="s">
+        <v>560</v>
+      </c>
+      <c r="AI139" s="59"/>
+      <c r="AJ139" s="59"/>
+      <c r="AK139" s="59"/>
+      <c r="AL139" s="59"/>
+      <c r="AM139" s="59"/>
+      <c r="AN139" s="59"/>
+      <c r="AO139" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="AD3" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="AZ3" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="4" spans="1:52" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="AD4" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="AZ4" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD5" s="11"/>
-      <c r="AZ5" s="11"/>
-    </row>
-    <row r="6" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD6" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="AZ6" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="AD7" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="AZ7" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="AP139" s="59"/>
+      <c r="AQ139" s="59"/>
+      <c r="AR139" s="59"/>
+      <c r="AS139" s="59"/>
+      <c r="AT139" s="59"/>
+      <c r="AU139" s="59"/>
+      <c r="AV139" s="59"/>
+      <c r="AW139" s="59"/>
+      <c r="AZ139" s="48" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="140" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="54" t="s">
+        <v>650</v>
+      </c>
+      <c r="AA140" s="60" t="s">
+        <v>561</v>
+      </c>
+      <c r="AB140" s="60"/>
+      <c r="AC140" s="60"/>
+      <c r="AD140" s="60"/>
+      <c r="AE140" s="60"/>
+      <c r="AF140" s="60"/>
+      <c r="AG140" s="60"/>
+      <c r="AH140" s="60" t="s">
+        <v>562</v>
+      </c>
+      <c r="AI140" s="60"/>
+      <c r="AJ140" s="60"/>
+      <c r="AK140" s="60"/>
+      <c r="AL140" s="60"/>
+      <c r="AM140" s="60"/>
+      <c r="AN140" s="60"/>
+      <c r="AO140" s="60" t="s">
+        <v>563</v>
+      </c>
+      <c r="AP140" s="60"/>
+      <c r="AQ140" s="60"/>
+      <c r="AR140" s="60"/>
+      <c r="AS140" s="60"/>
+      <c r="AT140" s="60"/>
+      <c r="AU140" s="60"/>
+      <c r="AV140" s="60"/>
+      <c r="AW140" s="60"/>
+      <c r="AZ140" s="48"/>
+    </row>
+    <row r="141" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="48" t="s">
+        <v>517</v>
+      </c>
+      <c r="AA141" s="60" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB141" s="60"/>
+      <c r="AC141" s="60"/>
+      <c r="AD141" s="60"/>
+      <c r="AE141" s="60"/>
+      <c r="AF141" s="60"/>
+      <c r="AG141" s="60"/>
+      <c r="AH141" s="60" t="s">
+        <v>565</v>
+      </c>
+      <c r="AI141" s="60"/>
+      <c r="AJ141" s="60"/>
+      <c r="AK141" s="60"/>
+      <c r="AL141" s="60"/>
+      <c r="AM141" s="60"/>
+      <c r="AN141" s="60"/>
+      <c r="AO141" s="60" t="s">
+        <v>566</v>
+      </c>
+      <c r="AP141" s="60"/>
+      <c r="AQ141" s="60"/>
+      <c r="AR141" s="60"/>
+      <c r="AS141" s="60"/>
+      <c r="AT141" s="60"/>
+      <c r="AU141" s="60"/>
+      <c r="AV141" s="60"/>
+      <c r="AW141" s="60"/>
+      <c r="AZ141" s="48" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="142" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="48"/>
+      <c r="AA142" s="60" t="s">
+        <v>567</v>
+      </c>
+      <c r="AB142" s="60"/>
+      <c r="AC142" s="60"/>
+      <c r="AD142" s="60"/>
+      <c r="AE142" s="60"/>
+      <c r="AF142" s="60"/>
+      <c r="AG142" s="60"/>
+      <c r="AH142" s="60" t="s">
+        <v>568</v>
+      </c>
+      <c r="AI142" s="60"/>
+      <c r="AJ142" s="60"/>
+      <c r="AK142" s="60"/>
+      <c r="AL142" s="60"/>
+      <c r="AM142" s="60"/>
+      <c r="AN142" s="60"/>
+      <c r="AO142" s="60" t="s">
+        <v>569</v>
+      </c>
+      <c r="AP142" s="60"/>
+      <c r="AQ142" s="60"/>
+      <c r="AR142" s="60"/>
+      <c r="AS142" s="60"/>
+      <c r="AT142" s="60"/>
+      <c r="AU142" s="60"/>
+      <c r="AV142" s="60"/>
+      <c r="AW142" s="60"/>
+      <c r="AZ142" s="48" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="143" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="48" t="s">
+        <v>553</v>
+      </c>
+      <c r="AA143" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="AB143" s="60"/>
+      <c r="AC143" s="60"/>
+      <c r="AD143" s="60"/>
+      <c r="AE143" s="60"/>
+      <c r="AF143" s="60"/>
+      <c r="AG143" s="60"/>
+      <c r="AH143" s="60" t="s">
+        <v>571</v>
+      </c>
+      <c r="AI143" s="60"/>
+      <c r="AJ143" s="60"/>
+      <c r="AK143" s="60"/>
+      <c r="AL143" s="60"/>
+      <c r="AM143" s="60"/>
+      <c r="AN143" s="60"/>
+      <c r="AO143" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="AP143" s="60"/>
+      <c r="AQ143" s="60"/>
+      <c r="AR143" s="60"/>
+      <c r="AS143" s="60"/>
+      <c r="AT143" s="60"/>
+      <c r="AU143" s="60"/>
+      <c r="AV143" s="60"/>
+      <c r="AW143" s="60"/>
+      <c r="AZ143" s="48" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="144" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="33" t="s">
+        <v>554</v>
+      </c>
+      <c r="AA144" s="60" t="s">
+        <v>573</v>
+      </c>
+      <c r="AB144" s="60"/>
+      <c r="AC144" s="60"/>
+      <c r="AD144" s="60"/>
+      <c r="AE144" s="60"/>
+      <c r="AF144" s="60"/>
+      <c r="AG144" s="60"/>
+      <c r="AH144" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="AI144" s="60"/>
+      <c r="AJ144" s="60"/>
+      <c r="AK144" s="60"/>
+      <c r="AL144" s="60"/>
+      <c r="AM144" s="60"/>
+      <c r="AN144" s="60"/>
+      <c r="AO144" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="AP144" s="60"/>
+      <c r="AQ144" s="60"/>
+      <c r="AR144" s="60"/>
+      <c r="AS144" s="60"/>
+      <c r="AT144" s="60"/>
+      <c r="AU144" s="60"/>
+      <c r="AV144" s="60"/>
+      <c r="AW144" s="60"/>
+      <c r="AZ144" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="145" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="48"/>
+      <c r="AZ145" s="48"/>
+    </row>
+    <row r="146" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="AZ146" s="48" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="147" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="48" t="s">
+        <v>556</v>
+      </c>
+      <c r="AZ147" s="48" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="148" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="48" t="s">
+        <v>557</v>
+      </c>
+      <c r="AZ148" s="48" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="149" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ149" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ150" s="48"/>
+    </row>
+    <row r="151" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ151" s="48" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="152" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ152" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="AD8" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AZ8" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD9" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ9" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="AD10" s="11" t="s">
+    </row>
+    <row r="153" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ153" s="48"/>
+    </row>
+    <row r="154" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ154" s="48" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="155" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ155" s="48" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="156" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ156" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ157" s="48"/>
+    </row>
+    <row r="158" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ158" s="48" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="159" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ159" s="48" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="160" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ160" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="32" t="s">
+        <v>588</v>
+      </c>
+      <c r="R161" s="32" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="48" t="s">
+        <v>589</v>
+      </c>
+      <c r="R162" s="48" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="R163" s="48" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="48" t="s">
+        <v>591</v>
+      </c>
+      <c r="R164" s="48"/>
+    </row>
+    <row r="165" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="48"/>
+      <c r="R165" s="48" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="48" t="s">
+        <v>592</v>
+      </c>
+      <c r="R166" s="48" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="48" t="s">
+        <v>593</v>
+      </c>
+      <c r="R167" s="48" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="48" t="s">
+        <v>594</v>
+      </c>
+      <c r="R168" s="48"/>
+    </row>
+    <row r="169" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="48"/>
+      <c r="R169" s="48" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="48" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="49" t="s">
+        <v>609</v>
+      </c>
+      <c r="R171" s="49" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="1:18" s="40" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="58" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="10" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="45" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="45" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="45" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="45" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="45" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="45" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="45" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="45" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="45" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="45" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="45" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="45" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="45" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="45" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="45" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="45" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="45" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="U195" s="50" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="32" t="s">
+        <v>676</v>
+      </c>
+      <c r="U196" s="50" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="U197" s="45" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="33" t="s">
+        <v>678</v>
+      </c>
+      <c r="U198" s="22" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="U199" s="50" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="45" t="s">
+        <v>586</v>
+      </c>
+      <c r="U200" s="51" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="50" t="s">
+        <v>680</v>
+      </c>
+      <c r="U201" s="51" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="50" t="s">
+        <v>681</v>
+      </c>
+      <c r="U202" s="51" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="50" t="s">
+        <v>682</v>
+      </c>
+      <c r="U203" s="51" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="50" t="s">
+        <v>586</v>
+      </c>
+      <c r="U204" s="51" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="30" t="s">
+        <v>683</v>
+      </c>
+      <c r="C205" s="54"/>
+      <c r="U205" s="28" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="C206" s="54"/>
+      <c r="U206" s="21" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="45" t="s">
+        <v>586</v>
+      </c>
+      <c r="U207" s="32" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="45" t="s">
+        <v>685</v>
+      </c>
+      <c r="U208" s="50" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="209" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="AZ10" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD11" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AZ11" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="AD12" s="11" t="s">
+      <c r="U209" s="51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="210" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="AZ12" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ13" s="11" t="s">
+      <c r="U210" s="51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="211" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="51"/>
+    </row>
+    <row r="212" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="51" t="s">
+        <v>694</v>
+      </c>
+      <c r="W212" s="7" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="213" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="51" t="s">
+        <v>695</v>
+      </c>
+      <c r="W213" s="45" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="214" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="W214" s="45" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="215" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="45" t="s">
+        <v>696</v>
+      </c>
+      <c r="W215" s="45" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="216" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="B216" s="21"/>
+      <c r="W216" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="217" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="45" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="218" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="B218" s="21"/>
+      <c r="W218" s="45" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="219" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="W219" s="45" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="45" t="s">
+        <v>700</v>
+      </c>
+      <c r="W220" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="X220" s="15"/>
+    </row>
+    <row r="221" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="45" t="s">
+        <v>586</v>
+      </c>
+      <c r="W221" s="45" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="222" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="B222" s="21"/>
+      <c r="W222" s="45" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="223" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="45" t="s">
+        <v>702</v>
+      </c>
+      <c r="W223" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="X223" s="15"/>
+    </row>
+    <row r="224" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="W224" s="45" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="45" t="s">
+        <v>704</v>
+      </c>
+      <c r="W225" s="45" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="45" t="s">
+        <v>705</v>
+      </c>
+      <c r="W226" s="45" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="45" t="s">
+        <v>706</v>
+      </c>
+      <c r="W227" s="45" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="45" t="s">
+        <v>707</v>
+      </c>
+      <c r="W228" s="45" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="45" t="s">
+        <v>708</v>
+      </c>
+      <c r="W229" s="45" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="45" t="s">
+        <v>705</v>
+      </c>
+      <c r="W230" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="45" t="s">
+        <v>706</v>
+      </c>
+      <c r="W231" s="45" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="45" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="45" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="45" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="45" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="45" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="45" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="45" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="45" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="45" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="45" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="45" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:52" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="AD14" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="AZ14" s="11" t="s">
+    <row r="243" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="45" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:52" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="AZ16" s="7" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="17" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD21" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AY21" s="14" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="AD22" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="AY22" s="7" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="23" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="AD23" s="7" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="24" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
-      <c r="AY24" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="AD25" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="AY25" s="11"/>
-    </row>
-    <row r="26" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD26" s="11"/>
-      <c r="AY26" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="AD27" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="AY27" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="28" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD28" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="AY28" s="11" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="29" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AD29" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="AY29" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AD30" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="AY30" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="31" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AD31" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="AY31" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="AD32" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="AY32" s="11" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="33" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AY33" s="11" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="34" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="AD34" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="AY34" s="11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AY35" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="36" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="AY36" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="37" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY37" s="11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="38" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AY38" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="40" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AY40" s="7" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="41" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="43" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="W44" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="AW44" s="14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="45" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="W45" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="AW45" s="14" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="46" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="AW46" s="7" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="47" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="W47" s="11" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
-      <c r="W48" s="11"/>
-      <c r="AW48" s="11" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="49" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="W49" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="AW49" s="11"/>
-    </row>
-    <row r="50" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="W50" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="AW50" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W51" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW51" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="52" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="W52" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AW52" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="53" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="W53" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="AW53" s="11"/>
-    </row>
-    <row r="54" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-      <c r="W54" s="11"/>
-      <c r="AW54" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="55" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="W55" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="AW55" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="W56" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="AW56" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="W57" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="AW57" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="58" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="W58" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="AW58" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="W59" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="AW59" s="11"/>
-    </row>
-    <row r="60" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="W60" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AW60" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="61" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AW61" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="62" spans="1:49" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="W62" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="AW62" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="63" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AW63" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="64" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AW64" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AW65" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="66" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AW66" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="1:49" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A68" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="AB68" s="14" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="69" spans="1:49" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="AB69" s="7" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="70" spans="1:49" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="71" spans="1:49" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="AB71" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="72" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AB72" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="73" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="AB73" s="11"/>
-    </row>
-    <row r="74" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB74" s="11" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB75" s="11" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="76" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="AB76" s="11"/>
-    </row>
-    <row r="77" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB77" s="11" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="78" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="AB78" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="79" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB79" s="11" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="80" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="AB80" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB82" s="7" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="11"/>
-    </row>
-    <row r="86" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="11" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="11" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="93" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="1:28" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="450" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="451" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="AA144:AG144"/>
+    <mergeCell ref="AA139:AG139"/>
+    <mergeCell ref="AA140:AG140"/>
+    <mergeCell ref="AA141:AG141"/>
+    <mergeCell ref="AA142:AG142"/>
+    <mergeCell ref="AA143:AG143"/>
+    <mergeCell ref="AO144:AW144"/>
+    <mergeCell ref="AH139:AN139"/>
+    <mergeCell ref="AH140:AN140"/>
+    <mergeCell ref="AH141:AN141"/>
+    <mergeCell ref="AH142:AN142"/>
+    <mergeCell ref="AH143:AN143"/>
+    <mergeCell ref="AH144:AN144"/>
+    <mergeCell ref="AO139:AW139"/>
+    <mergeCell ref="AO140:AW140"/>
+    <mergeCell ref="AO141:AW141"/>
+    <mergeCell ref="AO142:AW142"/>
+    <mergeCell ref="AO143:AW143"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT120"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BA120"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:44" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:49" s="18" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:44" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="V2" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="AR2" s="14" t="s">
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AR2" s="19" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="3" spans="1:44" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+    </row>
+    <row r="3" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="V3" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="AR3" s="7" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="V4" s="10" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>488</v>
+      <c r="V3" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="AR3" s="15" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>461</v>
       </c>
       <c r="V5" s="11" t="s">
         <v>267</v>
@@ -5072,36 +7343,36 @@
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="V6" s="11" t="s">
+      <c r="V6" s="16" t="s">
         <v>268</v>
       </c>
       <c r="AR6" s="11" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="7" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="V7" s="11" t="s">
         <v>269</v>
       </c>
       <c r="AR7" s="11"/>
     </row>
-    <row r="8" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="V8" s="16" t="s">
         <v>270</v>
       </c>
       <c r="AR8" s="11" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>260</v>
       </c>
@@ -5110,16 +7381,16 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
-      <c r="V10" s="11" t="s">
+      <c r="V10" s="16" t="s">
         <v>271</v>
       </c>
       <c r="AR10" s="11" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>144</v>
       </c>
@@ -5128,8 +7399,8 @@
       </c>
       <c r="AR11" s="11"/>
     </row>
-    <row r="12" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
         <v>261</v>
       </c>
       <c r="V12" s="11" t="s">
@@ -5139,8 +7410,8 @@
         <v>288</v>
       </c>
     </row>
-    <row r="13" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
         <v>262</v>
       </c>
       <c r="V13" s="11" t="s">
@@ -5150,7 +7421,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="14" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>50</v>
       </c>
@@ -5159,26 +7430,26 @@
         <v>290</v>
       </c>
     </row>
-    <row r="15" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
-      <c r="V15" s="11" t="s">
+      <c r="V15" s="16" t="s">
         <v>275</v>
       </c>
       <c r="AR15" s="11"/>
     </row>
-    <row r="16" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="V16" s="16" t="s">
         <v>276</v>
       </c>
       <c r="AR16" s="11" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="17" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
         <v>264</v>
       </c>
       <c r="V17" s="11"/>
@@ -5186,101 +7457,126 @@
         <v>292</v>
       </c>
     </row>
-    <row r="18" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="V18" s="11" t="s">
+      <c r="V18" s="16" t="s">
         <v>277</v>
       </c>
+      <c r="W18" s="21"/>
       <c r="AR18" s="11" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="V19" s="16" t="s">
         <v>278</v>
       </c>
+      <c r="W19" s="21"/>
       <c r="AR19" s="7" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="20" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="V20" s="11" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="20" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="V20" s="16" t="s">
         <v>279</v>
       </c>
+      <c r="W20" s="21"/>
       <c r="AR20" s="11" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="21" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="V21" s="11" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="21" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V21" s="16" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="22" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="V22" s="11" t="s">
+      <c r="W21" s="21"/>
+    </row>
+    <row r="22" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V22" s="16" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="23" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="14" t="s">
+      <c r="W22" s="21"/>
+    </row>
+    <row r="23" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="W24" s="14" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="W24" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="AT24" s="14" t="s">
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AT24" s="19" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="25" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>475</v>
+      <c r="AU24" s="20"/>
+      <c r="AV24" s="20"/>
+      <c r="AW24" s="20"/>
+      <c r="AX24" s="20"/>
+      <c r="AY24" s="20"/>
+      <c r="AZ24" s="20"/>
+      <c r="BA24" s="20"/>
+    </row>
+    <row r="25" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>658</v>
       </c>
       <c r="W25" s="14" t="s">
         <v>306</v>
       </c>
       <c r="AT25" s="7" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="26" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>476</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="26" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>451</v>
       </c>
       <c r="W26" s="7" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="AT26" s="11" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="27" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W27" s="10" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="AT27" s="11" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="28" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+    <row r="28" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>295</v>
       </c>
       <c r="AT28" s="11" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
         <v>278</v>
       </c>
       <c r="W29" s="11" t="s">
@@ -5290,8 +7586,8 @@
         <v>327</v>
       </c>
     </row>
-    <row r="30" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+    <row r="30" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
         <v>296</v>
       </c>
       <c r="W30" s="11" t="s">
@@ -5301,14 +7597,14 @@
         <v>328</v>
       </c>
     </row>
-    <row r="31" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="W31" s="11"/>
       <c r="AT31" s="11" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="32" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:53" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>297</v>
       </c>
@@ -5319,8 +7615,8 @@
         <v>330</v>
       </c>
     </row>
-    <row r="33" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+    <row r="33" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="33" t="s">
         <v>298</v>
       </c>
       <c r="W33" s="11" t="s">
@@ -5330,7 +7626,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>299</v>
       </c>
@@ -5339,7 +7635,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="35" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>300</v>
       </c>
@@ -5350,7 +7646,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>301</v>
       </c>
@@ -5361,27 +7657,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>50</v>
       </c>
       <c r="W37" s="7" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="AT37" s="11" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="W38" s="11" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="AT38" s="11" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="39" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>302</v>
       </c>
@@ -5389,7 +7685,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="40" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>303</v>
       </c>
@@ -5400,29 +7696,29 @@
         <v>335</v>
       </c>
     </row>
-    <row r="41" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>304</v>
       </c>
       <c r="W41" s="7" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
       <c r="AT41" s="11" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="42" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>50</v>
       </c>
       <c r="W42" s="10" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="AT42" s="11" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="43" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W43" s="11" t="s">
         <v>314</v>
       </c>
@@ -5430,9 +7726,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="W44" s="11" t="s">
         <v>315</v>
@@ -5441,7 +7737,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W45" s="11" t="s">
         <v>316</v>
       </c>
@@ -5449,7 +7745,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="46" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W46" s="11" t="s">
         <v>317</v>
       </c>
@@ -5457,13 +7753,13 @@
         <v>339</v>
       </c>
     </row>
-    <row r="47" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W47" s="11"/>
       <c r="AT47" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W48" s="11" t="s">
         <v>318</v>
       </c>
@@ -5471,7 +7767,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="49" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W49" s="11" t="s">
         <v>319</v>
       </c>
@@ -5479,7 +7775,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="50" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W50" s="11" t="s">
         <v>320</v>
       </c>
@@ -5487,7 +7783,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="51" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W51" s="11" t="s">
         <v>321</v>
       </c>
@@ -5495,7 +7791,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="52" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W52" s="11" t="s">
         <v>61</v>
       </c>
@@ -5503,13 +7799,13 @@
         <v>344</v>
       </c>
     </row>
-    <row r="53" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W53" s="11"/>
       <c r="AT53" s="11" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="54" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="W54" s="11" t="s">
         <v>322</v>
       </c>
@@ -5517,534 +7813,1104 @@
         <v>346</v>
       </c>
     </row>
-    <row r="55" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT55" s="11" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="56" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT56" s="11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="57" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT57" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT58" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="23:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT60" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT61" s="12" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="62" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT62" s="12" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="63" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT63" s="12" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="64" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" spans="46:46" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="23:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AT65" s="7" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="66" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="66" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="46:46" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AY93"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AY94"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:30" s="18" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="57" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+    </row>
+    <row r="3" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+    </row>
+    <row r="4" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
+        <v>506</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="43"/>
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="43"/>
+      <c r="AD4" s="43"/>
+    </row>
+    <row r="5" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
+        <v>507</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="43"/>
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="43"/>
+      <c r="AD5" s="43"/>
+    </row>
+    <row r="6" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="43"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="43"/>
+    </row>
+    <row r="7" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
+        <v>495</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
+      <c r="Z7" s="43"/>
+      <c r="AA7" s="43"/>
+      <c r="AB7" s="43"/>
+      <c r="AC7" s="43"/>
+      <c r="AD7" s="43"/>
+    </row>
+    <row r="8" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="38" t="s">
+        <v>508</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
+      <c r="Z8" s="43"/>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="43"/>
+      <c r="AC8" s="43"/>
+      <c r="AD8" s="43"/>
+    </row>
+    <row r="9" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="38" t="s">
+        <v>509</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
+      <c r="Z9" s="43"/>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="43"/>
+    </row>
+    <row r="10" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="38" t="s">
+        <v>510</v>
+      </c>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="43"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="43"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="43"/>
+      <c r="AD10" s="43"/>
+    </row>
+    <row r="11" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="38" t="s">
+        <v>511</v>
+      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
+      <c r="Z11" s="43"/>
+      <c r="AA11" s="43"/>
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="43"/>
+      <c r="AD11" s="43"/>
+    </row>
+    <row r="12" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+    </row>
+    <row r="13" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
+        <v>502</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="43"/>
+    </row>
+    <row r="14" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43" t="s">
+        <v>512</v>
+      </c>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="43"/>
+      <c r="Z14" s="43"/>
+      <c r="AA14" s="43"/>
+      <c r="AB14" s="43"/>
+      <c r="AC14" s="43"/>
+      <c r="AD14" s="43"/>
+    </row>
+    <row r="15" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43" t="s">
+        <v>513</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="43"/>
+      <c r="Z15" s="43"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="43"/>
+      <c r="AD15" s="43"/>
+    </row>
+    <row r="16" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="43"/>
+      <c r="Z16" s="43"/>
+      <c r="AA16" s="43"/>
+      <c r="AB16" s="43"/>
+      <c r="AC16" s="43"/>
+      <c r="AD16" s="43"/>
+    </row>
+    <row r="17" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
+      <c r="B17" s="45" t="s">
+        <v>514</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="43"/>
+      <c r="Y17" s="43"/>
+      <c r="Z17" s="43"/>
+      <c r="AA17" s="43"/>
+      <c r="AB17" s="43"/>
+      <c r="AC17" s="43"/>
+      <c r="AD17" s="43"/>
+    </row>
+    <row r="18" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="43"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="43"/>
+      <c r="Z18" s="43"/>
+      <c r="AA18" s="43"/>
+      <c r="AB18" s="43"/>
+      <c r="AC18" s="43"/>
+      <c r="AD18" s="43"/>
+    </row>
+    <row r="19" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="3" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="AD3" s="14" t="s">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="AD20" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="AY3" s="14" t="s">
+      <c r="AY20" s="14" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="AD4" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="AY4" s="7" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="AD5" s="11" t="s">
+    <row r="21" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="AD21" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="AY21" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="AD22" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="AY5" s="10" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="AY22" s="10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="AD6" s="11"/>
-      <c r="AY6" s="11" t="s">
+      <c r="AD23" s="11"/>
+      <c r="AY23" s="11" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="AD7" s="11" t="s">
+    <row r="24" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="AD24" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="AY7" s="11" t="s">
+      <c r="AY24" s="11" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+    <row r="25" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="AD8" s="11" t="s">
+      <c r="AD25" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="AY8" s="11" t="s">
+      <c r="AY25" s="11" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+    <row r="26" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="AD9" s="11" t="s">
+      <c r="AD26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AY9" s="11" t="s">
+      <c r="AY26" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+    <row r="27" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="AD10" s="11"/>
-      <c r="AY10" s="11"/>
-    </row>
-    <row r="11" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="AD11" s="11" t="s">
+      <c r="AD27" s="11"/>
+      <c r="AY27" s="11"/>
+    </row>
+    <row r="28" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="11"/>
+      <c r="AD28" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="AY11" s="11" t="s">
+      <c r="AY28" s="11" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="12" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+    <row r="29" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="AD12" s="11" t="s">
+      <c r="AD29" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="AY12" s="11" t="s">
+      <c r="AY29" s="11" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+    <row r="30" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="AD13" s="11"/>
-      <c r="AY13" s="11"/>
-    </row>
-    <row r="14" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="AD30" s="11"/>
+      <c r="AY30" s="11"/>
+    </row>
+    <row r="31" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AD14" s="11" t="s">
+      <c r="AD31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="AY14" s="11" t="s">
+      <c r="AY31" s="11" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="15" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+    <row r="32" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="AD15" s="11" t="s">
+      <c r="AD32" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="AY15" s="11" t="s">
+      <c r="AY32" s="11" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="16" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+    <row r="33" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AD16" s="11"/>
-      <c r="AY16" s="11"/>
-    </row>
-    <row r="17" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="AD17" s="11" t="s">
+      <c r="AD33" s="11"/>
+      <c r="AY33" s="11"/>
+    </row>
+    <row r="34" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="AD34" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="AY17" s="11" t="s">
+      <c r="AY34" s="11" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+    <row r="35" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="AD18" s="11" t="s">
+      <c r="AD35" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="AY18" s="11" t="s">
+      <c r="AY35" s="11" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="19" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+    <row r="36" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="AD19" s="11"/>
-      <c r="AY19" s="11" t="s">
+      <c r="AD36" s="11"/>
+      <c r="AY36" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+    <row r="37" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="AD20" s="11" t="s">
+      <c r="AD37" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AY20" s="7" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="21" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD21" s="11" t="s">
+      <c r="AY37" s="7" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="38" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD38" s="11" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="22" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="AD22" s="11" t="s">
+    <row r="39" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="AD39" s="11" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="23" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD23" s="11" t="s">
+    <row r="40" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD40" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="AD25" s="7" t="s">
+    <row r="41" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD42" s="7" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="26" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD26" s="12" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="27" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD27" s="12" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="28" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD28" s="12" t="s">
+    <row r="43" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD43" s="12" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="44" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD44" s="12" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="45" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD45" s="12" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="29" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AD29" s="12"/>
-    </row>
-    <row r="30" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
+    <row r="46" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD46" s="12"/>
+    </row>
+    <row r="47" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="AC30" s="14" t="s">
+      <c r="AC47" s="14" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="31" spans="1:51" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="AC31" s="8" t="s">
+    <row r="48" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC48" s="8" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="32" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+    <row r="49" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="AC32" s="13" t="s">
+      <c r="AC49" s="13" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+    <row r="50" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="AC33" s="13" t="s">
+      <c r="AC50" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="34" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="AC34" s="9" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
+    <row r="51" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="11"/>
+      <c r="AC51" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="AC35" s="12"/>
-    </row>
-    <row r="36" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="AC52" s="12"/>
+    </row>
+    <row r="53" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="AC36" s="8" t="s">
+      <c r="AC53" s="8" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
+    <row r="54" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="AC37" s="13" t="s">
+      <c r="AC54" s="13" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
+    <row r="55" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AC38" s="9" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="AC39" s="12"/>
-    </row>
-    <row r="40" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
+      <c r="AC55" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="11"/>
+      <c r="AC56" s="12"/>
+    </row>
+    <row r="57" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="AC40" s="8" t="s">
+      <c r="AC57" s="8" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
+    <row r="58" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="AC41" s="13" t="s">
+      <c r="AC58" s="13" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="11" t="s">
+    <row r="59" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AC42" s="9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="AC43" s="12"/>
-    </row>
-    <row r="44" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="11" t="s">
+      <c r="AC59" s="9" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="AC60" s="12"/>
+    </row>
+    <row r="61" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="AC44" s="8" t="s">
+      <c r="AC61" s="8" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="45" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
+    <row r="62" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="AC45" s="13" t="s">
+      <c r="AC62" s="13" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46" s="11" t="s">
+    <row r="63" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="AC46" s="9" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="47" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AC47" s="12"/>
-    </row>
-    <row r="48" spans="1:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC48" s="8" t="s">
+      <c r="AC63" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC64" s="12"/>
+    </row>
+    <row r="65" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC65" s="8" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="49" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="AC49" s="13" t="s">
+    <row r="66" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC66" s="13" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="50" spans="29:29" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="AC50" s="9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="51" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="29:29" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="10" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC67" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
